--- a/excel_routes/route_ELQ_CAI_threats.xlsx
+++ b/excel_routes/route_ELQ_CAI_threats.xlsx
@@ -33,7 +33,7 @@
       <b val="1"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
@@ -50,18 +50,6 @@
       <patternFill patternType="solid">
         <fgColor rgb="00D4EDDA"/>
         <bgColor rgb="00D4EDDA"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFF3CD"/>
-        <bgColor rgb="00FFF3CD"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00F8D7DA"/>
-        <bgColor rgb="00F8D7DA"/>
       </patternFill>
     </fill>
   </fills>
@@ -83,7 +71,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -92,12 +80,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -465,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K36"/>
+  <dimension ref="A1:K21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -541,12 +523,12 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>03-JUN-26</t>
+          <t>28-JUL-26</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>SM-2428</t>
+          <t>SM-428</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -558,10 +540,10 @@
         <v>400</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>412</v>
+        <v>380</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>-12</v>
+        <v>20</v>
       </c>
       <c r="G2" s="2" t="n">
         <v>40</v>
@@ -586,12 +568,12 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>03-JUN-26</t>
+          <t>28-JUL-26</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>SM-2428</t>
+          <t>SM-428</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -603,10 +585,10 @@
         <v>401</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>412</v>
+        <v>380</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>-11</v>
+        <v>21</v>
       </c>
       <c r="G3" s="2" t="n">
         <v>40</v>
@@ -631,7 +613,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>05-JUN-26</t>
+          <t>29-JUL-26</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
@@ -641,17 +623,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-143</t>
+          <t>Nesma Airlines NE-141</t>
         </is>
       </c>
       <c r="D4" s="2" t="n">
-        <v>400</v>
+        <v>350</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>519</v>
+        <v>380</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>-119</v>
+        <v>-30</v>
       </c>
       <c r="G4" s="2" t="n">
         <v>40</v>
@@ -662,9 +644,9 @@
       <c r="I4" s="2" t="n">
         <v>-10</v>
       </c>
-      <c r="J4" s="4" t="inlineStr">
-        <is>
-          <t>MED</t>
+      <c r="J4" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -676,7 +658,7 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>05-JUN-26</t>
+          <t>29-JUL-26</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
@@ -690,13 +672,13 @@
         </is>
       </c>
       <c r="D5" s="2" t="n">
-        <v>500</v>
+        <v>401</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>519</v>
+        <v>380</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>-19</v>
+        <v>21</v>
       </c>
       <c r="G5" s="2" t="n">
         <v>40</v>
@@ -721,7 +703,7 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>09-JUN-26</t>
+          <t>31-JUL-26</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
@@ -731,17 +713,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-141</t>
+          <t>Nile Air NP-116</t>
         </is>
       </c>
       <c r="D6" s="2" t="n">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>412</v>
+        <v>400</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>-12</v>
+        <v>1</v>
       </c>
       <c r="G6" s="2" t="n">
         <v>40</v>
@@ -766,7 +748,7 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>09-JUN-26</t>
+          <t>31-JUL-26</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
@@ -783,10 +765,10 @@
         <v>500</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>412</v>
+        <v>400</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>88</v>
+        <v>100</v>
       </c>
       <c r="G7" s="2" t="n">
         <v>40</v>
@@ -811,7 +793,7 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>09-JUN-26</t>
+          <t>04-AUG-26</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
@@ -821,26 +803,26 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-634</t>
+          <t>Nesma Airlines NE-141</t>
         </is>
       </c>
       <c r="D8" s="2" t="n">
-        <v>610</v>
+        <v>400</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>412</v>
+        <v>400</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>198</v>
+        <v>0</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="H8" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>-16</v>
+        <v>-10</v>
       </c>
       <c r="J8" s="3" t="inlineStr">
         <is>
@@ -856,7 +838,7 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>10-JUN-26</t>
+          <t>04-AUG-26</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
@@ -866,17 +848,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-141</t>
+          <t>Nile Air NP-116</t>
         </is>
       </c>
       <c r="D9" s="2" t="n">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>412</v>
+        <v>400</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>-12</v>
+        <v>1</v>
       </c>
       <c r="G9" s="2" t="n">
         <v>40</v>
@@ -901,7 +883,7 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>10-JUN-26</t>
+          <t>04-AUG-26</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
@@ -918,10 +900,10 @@
         <v>401</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>412</v>
+        <v>400</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>-11</v>
+        <v>1</v>
       </c>
       <c r="G10" s="2" t="n">
         <v>40</v>
@@ -946,7 +928,7 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>12-JUN-26</t>
+          <t>05-AUG-26</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
@@ -956,17 +938,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-143</t>
+          <t>Nesma Airlines NE-141</t>
         </is>
       </c>
       <c r="D11" s="2" t="n">
-        <v>450</v>
+        <v>400</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>519</v>
+        <v>400</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>-69</v>
+        <v>0</v>
       </c>
       <c r="G11" s="2" t="n">
         <v>40</v>
@@ -977,9 +959,9 @@
       <c r="I11" s="2" t="n">
         <v>-10</v>
       </c>
-      <c r="J11" s="4" t="inlineStr">
-        <is>
-          <t>MED</t>
+      <c r="J11" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -991,7 +973,7 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>12-JUN-26</t>
+          <t>05-AUG-26</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
@@ -1008,10 +990,10 @@
         <v>500</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>519</v>
+        <v>400</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>-19</v>
+        <v>100</v>
       </c>
       <c r="G12" s="2" t="n">
         <v>40</v>
@@ -1036,7 +1018,7 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>16-JUN-26</t>
+          <t>05-AUG-26</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
@@ -1046,26 +1028,26 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-141</t>
+          <t>EgyptAir MS-634</t>
         </is>
       </c>
       <c r="D13" s="2" t="n">
-        <v>550</v>
+        <v>531</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>579</v>
+        <v>400</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>-29</v>
+        <v>131</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="H13" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>-10</v>
+        <v>-16</v>
       </c>
       <c r="J13" s="3" t="inlineStr">
         <is>
@@ -1081,7 +1063,7 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>16-JUN-26</t>
+          <t>07-AUG-26</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
@@ -1091,17 +1073,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-106</t>
+          <t>Nile Air NP-116</t>
         </is>
       </c>
       <c r="D14" s="2" t="n">
-        <v>550</v>
+        <v>401</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>579</v>
+        <v>400</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>-29</v>
+        <v>1</v>
       </c>
       <c r="G14" s="2" t="n">
         <v>40</v>
@@ -1126,7 +1108,7 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>17-JUN-26</t>
+          <t>07-AUG-26</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
@@ -1136,26 +1118,26 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-141</t>
+          <t>Nile Air NP-106</t>
         </is>
       </c>
       <c r="D15" s="2" t="n">
-        <v>600</v>
+        <v>401</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>639</v>
+        <v>400</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>-39</v>
+        <v>1</v>
       </c>
       <c r="G15" s="2" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="H15" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I15" s="2" t="n">
-        <v>0</v>
+        <v>-10</v>
       </c>
       <c r="J15" s="3" t="inlineStr">
         <is>
@@ -1171,7 +1153,7 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>23-JUN-26</t>
+          <t>11-AUG-26</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
@@ -1185,22 +1167,22 @@
         </is>
       </c>
       <c r="D16" s="2" t="n">
-        <v>845</v>
+        <v>400</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>849</v>
+        <v>380</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>-4</v>
+        <v>20</v>
       </c>
       <c r="G16" s="2" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="H16" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>0</v>
+        <v>-10</v>
       </c>
       <c r="J16" s="3" t="inlineStr">
         <is>
@@ -1216,7 +1198,7 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>24-JUN-26</t>
+          <t>11-AUG-26</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
@@ -1226,26 +1208,26 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-141</t>
+          <t>Nile Air NP-106</t>
         </is>
       </c>
       <c r="D17" s="2" t="n">
-        <v>845</v>
+        <v>500</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>849</v>
+        <v>380</v>
       </c>
       <c r="F17" s="2" t="n">
-        <v>-4</v>
+        <v>120</v>
       </c>
       <c r="G17" s="2" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="H17" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I17" s="2" t="n">
-        <v>0</v>
+        <v>-10</v>
       </c>
       <c r="J17" s="3" t="inlineStr">
         <is>
@@ -1261,7 +1243,7 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>30-JUN-26</t>
+          <t>12-AUG-26</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
@@ -1275,22 +1257,22 @@
         </is>
       </c>
       <c r="D18" s="2" t="n">
-        <v>950</v>
+        <v>400</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>1059</v>
+        <v>380</v>
       </c>
       <c r="F18" s="2" t="n">
-        <v>-109</v>
+        <v>20</v>
       </c>
       <c r="G18" s="2" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="H18" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v>0</v>
+        <v>-10</v>
       </c>
       <c r="J18" s="3" t="inlineStr">
         <is>
@@ -1306,7 +1288,7 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>30-JUN-26</t>
+          <t>12-AUG-26</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
@@ -1316,30 +1298,30 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-634</t>
+          <t>Nile Air NP-106</t>
         </is>
       </c>
       <c r="D19" s="2" t="n">
-        <v>1075</v>
+        <v>401</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>1059</v>
+        <v>380</v>
       </c>
       <c r="F19" s="2" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="G19" s="2" t="n">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="H19" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I19" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J19" s="4" t="inlineStr">
-        <is>
-          <t>MED</t>
+        <v>-10</v>
+      </c>
+      <c r="J19" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
@@ -1351,7 +1333,7 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>01-JUL-26</t>
+          <t>14-AUG-26</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
@@ -1361,26 +1343,26 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-634</t>
+          <t>Nile Air NP-116</t>
         </is>
       </c>
       <c r="D20" s="2" t="n">
-        <v>1075</v>
+        <v>401</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>849</v>
+        <v>400</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>226</v>
+        <v>1</v>
       </c>
       <c r="G20" s="2" t="n">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="H20" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I20" s="2" t="n">
-        <v>-16</v>
+        <v>-10</v>
       </c>
       <c r="J20" s="3" t="inlineStr">
         <is>
@@ -1396,7 +1378,7 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>03-JUL-26</t>
+          <t>14-AUG-26</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
@@ -1406,26 +1388,26 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-634</t>
+          <t>Nile Air NP-106</t>
         </is>
       </c>
       <c r="D21" s="2" t="n">
-        <v>1075</v>
+        <v>500</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>849</v>
+        <v>400</v>
       </c>
       <c r="F21" s="2" t="n">
-        <v>226</v>
+        <v>100</v>
       </c>
       <c r="G21" s="2" t="n">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="H21" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I21" s="2" t="n">
-        <v>-16</v>
+        <v>-10</v>
       </c>
       <c r="J21" s="3" t="inlineStr">
         <is>
@@ -1433,681 +1415,6 @@
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>SAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>08-JUL-26</t>
-        </is>
-      </c>
-      <c r="B22" s="2" t="inlineStr">
-        <is>
-          <t>SM-428</t>
-        </is>
-      </c>
-      <c r="C22" s="2" t="inlineStr">
-        <is>
-          <t>EgyptAir MS-634</t>
-        </is>
-      </c>
-      <c r="D22" s="2" t="n">
-        <v>1075</v>
-      </c>
-      <c r="E22" s="2" t="n">
-        <v>849</v>
-      </c>
-      <c r="F22" s="2" t="n">
-        <v>226</v>
-      </c>
-      <c r="G22" s="2" t="n">
-        <v>46</v>
-      </c>
-      <c r="H22" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I22" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J22" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="K22" s="2" t="inlineStr">
-        <is>
-          <t>SAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="2" t="inlineStr">
-        <is>
-          <t>10-JUL-26</t>
-        </is>
-      </c>
-      <c r="B23" s="2" t="inlineStr">
-        <is>
-          <t>SM-428</t>
-        </is>
-      </c>
-      <c r="C23" s="2" t="inlineStr">
-        <is>
-          <t>EgyptAir MS-634</t>
-        </is>
-      </c>
-      <c r="D23" s="2" t="n">
-        <v>940</v>
-      </c>
-      <c r="E23" s="2" t="n">
-        <v>849</v>
-      </c>
-      <c r="F23" s="2" t="n">
-        <v>91</v>
-      </c>
-      <c r="G23" s="2" t="n">
-        <v>46</v>
-      </c>
-      <c r="H23" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I23" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J23" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>SAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="2" t="inlineStr">
-        <is>
-          <t>14-JUL-26</t>
-        </is>
-      </c>
-      <c r="B24" s="2" t="inlineStr">
-        <is>
-          <t>SM-428</t>
-        </is>
-      </c>
-      <c r="C24" s="2" t="inlineStr">
-        <is>
-          <t>EgyptAir MS-634</t>
-        </is>
-      </c>
-      <c r="D24" s="2" t="n">
-        <v>820</v>
-      </c>
-      <c r="E24" s="2" t="n">
-        <v>849</v>
-      </c>
-      <c r="F24" s="2" t="n">
-        <v>-29</v>
-      </c>
-      <c r="G24" s="2" t="n">
-        <v>46</v>
-      </c>
-      <c r="H24" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I24" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J24" s="4" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="K24" s="2" t="inlineStr">
-        <is>
-          <t>SAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="2" t="inlineStr">
-        <is>
-          <t>15-JUL-26</t>
-        </is>
-      </c>
-      <c r="B25" s="2" t="inlineStr">
-        <is>
-          <t>SM-428</t>
-        </is>
-      </c>
-      <c r="C25" s="2" t="inlineStr">
-        <is>
-          <t>EgyptAir MS-634</t>
-        </is>
-      </c>
-      <c r="D25" s="2" t="n">
-        <v>730</v>
-      </c>
-      <c r="E25" s="2" t="n">
-        <v>849</v>
-      </c>
-      <c r="F25" s="2" t="n">
-        <v>-119</v>
-      </c>
-      <c r="G25" s="2" t="n">
-        <v>46</v>
-      </c>
-      <c r="H25" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I25" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J25" s="4" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="K25" s="2" t="inlineStr">
-        <is>
-          <t>SAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="2" t="inlineStr">
-        <is>
-          <t>17-JUL-26</t>
-        </is>
-      </c>
-      <c r="B26" s="2" t="inlineStr">
-        <is>
-          <t>SM-428</t>
-        </is>
-      </c>
-      <c r="C26" s="2" t="inlineStr">
-        <is>
-          <t>EgyptAir MS-634</t>
-        </is>
-      </c>
-      <c r="D26" s="2" t="n">
-        <v>610</v>
-      </c>
-      <c r="E26" s="2" t="n">
-        <v>849</v>
-      </c>
-      <c r="F26" s="2" t="n">
-        <v>-239</v>
-      </c>
-      <c r="G26" s="2" t="n">
-        <v>46</v>
-      </c>
-      <c r="H26" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I26" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J26" s="5" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="K26" s="2" t="inlineStr">
-        <is>
-          <t>SAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="2" t="inlineStr">
-        <is>
-          <t>17-JUL-26</t>
-        </is>
-      </c>
-      <c r="B27" s="2" t="inlineStr">
-        <is>
-          <t>SM-428</t>
-        </is>
-      </c>
-      <c r="C27" s="2" t="inlineStr">
-        <is>
-          <t>Nile Air NP-116</t>
-        </is>
-      </c>
-      <c r="D27" s="2" t="n">
-        <v>650</v>
-      </c>
-      <c r="E27" s="2" t="n">
-        <v>849</v>
-      </c>
-      <c r="F27" s="2" t="n">
-        <v>-199</v>
-      </c>
-      <c r="G27" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="H27" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I27" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J27" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="K27" s="2" t="inlineStr">
-        <is>
-          <t>SAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="2" t="inlineStr">
-        <is>
-          <t>21-JUL-26</t>
-        </is>
-      </c>
-      <c r="B28" s="2" t="inlineStr">
-        <is>
-          <t>SM-428</t>
-        </is>
-      </c>
-      <c r="C28" s="2" t="inlineStr">
-        <is>
-          <t>Nile Air NP-106</t>
-        </is>
-      </c>
-      <c r="D28" s="2" t="n">
-        <v>550</v>
-      </c>
-      <c r="E28" s="2" t="n">
-        <v>579</v>
-      </c>
-      <c r="F28" s="2" t="n">
-        <v>-29</v>
-      </c>
-      <c r="G28" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="H28" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I28" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J28" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="K28" s="2" t="inlineStr">
-        <is>
-          <t>SAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="2" t="inlineStr">
-        <is>
-          <t>22-JUL-26</t>
-        </is>
-      </c>
-      <c r="B29" s="2" t="inlineStr">
-        <is>
-          <t>SM-428</t>
-        </is>
-      </c>
-      <c r="C29" s="2" t="inlineStr">
-        <is>
-          <t>Nesma Airlines NE-141</t>
-        </is>
-      </c>
-      <c r="D29" s="2" t="n">
-        <v>550</v>
-      </c>
-      <c r="E29" s="2" t="n">
-        <v>579</v>
-      </c>
-      <c r="F29" s="2" t="n">
-        <v>-29</v>
-      </c>
-      <c r="G29" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="H29" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I29" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J29" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="K29" s="2" t="inlineStr">
-        <is>
-          <t>SAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="2" t="inlineStr">
-        <is>
-          <t>22-JUL-26</t>
-        </is>
-      </c>
-      <c r="B30" s="2" t="inlineStr">
-        <is>
-          <t>SM-428</t>
-        </is>
-      </c>
-      <c r="C30" s="2" t="inlineStr">
-        <is>
-          <t>Nile Air NP-106</t>
-        </is>
-      </c>
-      <c r="D30" s="2" t="n">
-        <v>550</v>
-      </c>
-      <c r="E30" s="2" t="n">
-        <v>579</v>
-      </c>
-      <c r="F30" s="2" t="n">
-        <v>-29</v>
-      </c>
-      <c r="G30" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="H30" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I30" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J30" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="K30" s="2" t="inlineStr">
-        <is>
-          <t>SAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="2" t="inlineStr">
-        <is>
-          <t>24-JUL-26</t>
-        </is>
-      </c>
-      <c r="B31" s="2" t="inlineStr">
-        <is>
-          <t>SM-428</t>
-        </is>
-      </c>
-      <c r="C31" s="2" t="inlineStr">
-        <is>
-          <t>Nile Air NP-116</t>
-        </is>
-      </c>
-      <c r="D31" s="2" t="n">
-        <v>550</v>
-      </c>
-      <c r="E31" s="2" t="n">
-        <v>579</v>
-      </c>
-      <c r="F31" s="2" t="n">
-        <v>-29</v>
-      </c>
-      <c r="G31" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="H31" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I31" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J31" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="K31" s="2" t="inlineStr">
-        <is>
-          <t>SAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="2" t="inlineStr">
-        <is>
-          <t>24-JUL-26</t>
-        </is>
-      </c>
-      <c r="B32" s="2" t="inlineStr">
-        <is>
-          <t>SM-428</t>
-        </is>
-      </c>
-      <c r="C32" s="2" t="inlineStr">
-        <is>
-          <t>Nile Air NP-106</t>
-        </is>
-      </c>
-      <c r="D32" s="2" t="n">
-        <v>550</v>
-      </c>
-      <c r="E32" s="2" t="n">
-        <v>579</v>
-      </c>
-      <c r="F32" s="2" t="n">
-        <v>-29</v>
-      </c>
-      <c r="G32" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="H32" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I32" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J32" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="K32" s="2" t="inlineStr">
-        <is>
-          <t>SAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="2" t="inlineStr">
-        <is>
-          <t>28-JUL-26</t>
-        </is>
-      </c>
-      <c r="B33" s="2" t="inlineStr">
-        <is>
-          <t>SM-428</t>
-        </is>
-      </c>
-      <c r="C33" s="2" t="inlineStr">
-        <is>
-          <t>Nile Air NP-106</t>
-        </is>
-      </c>
-      <c r="D33" s="2" t="n">
-        <v>550</v>
-      </c>
-      <c r="E33" s="2" t="n">
-        <v>579</v>
-      </c>
-      <c r="F33" s="2" t="n">
-        <v>-29</v>
-      </c>
-      <c r="G33" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="H33" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I33" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J33" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="K33" s="2" t="inlineStr">
-        <is>
-          <t>SAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="2" t="inlineStr">
-        <is>
-          <t>29-JUL-26</t>
-        </is>
-      </c>
-      <c r="B34" s="2" t="inlineStr">
-        <is>
-          <t>SM-428</t>
-        </is>
-      </c>
-      <c r="C34" s="2" t="inlineStr">
-        <is>
-          <t>Nile Air NP-106</t>
-        </is>
-      </c>
-      <c r="D34" s="2" t="n">
-        <v>550</v>
-      </c>
-      <c r="E34" s="2" t="n">
-        <v>579</v>
-      </c>
-      <c r="F34" s="2" t="n">
-        <v>-29</v>
-      </c>
-      <c r="G34" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="H34" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I34" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J34" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="K34" s="2" t="inlineStr">
-        <is>
-          <t>SAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="2" t="inlineStr">
-        <is>
-          <t>31-JUL-26</t>
-        </is>
-      </c>
-      <c r="B35" s="2" t="inlineStr">
-        <is>
-          <t>SM-428</t>
-        </is>
-      </c>
-      <c r="C35" s="2" t="inlineStr">
-        <is>
-          <t>Nile Air NP-116</t>
-        </is>
-      </c>
-      <c r="D35" s="2" t="n">
-        <v>550</v>
-      </c>
-      <c r="E35" s="2" t="n">
-        <v>579</v>
-      </c>
-      <c r="F35" s="2" t="n">
-        <v>-29</v>
-      </c>
-      <c r="G35" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="H35" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I35" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J35" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="K35" s="2" t="inlineStr">
-        <is>
-          <t>SAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="2" t="inlineStr">
-        <is>
-          <t>31-JUL-26</t>
-        </is>
-      </c>
-      <c r="B36" s="2" t="inlineStr">
-        <is>
-          <t>SM-428</t>
-        </is>
-      </c>
-      <c r="C36" s="2" t="inlineStr">
-        <is>
-          <t>Nile Air NP-106</t>
-        </is>
-      </c>
-      <c r="D36" s="2" t="n">
-        <v>550</v>
-      </c>
-      <c r="E36" s="2" t="n">
-        <v>579</v>
-      </c>
-      <c r="F36" s="2" t="n">
-        <v>-29</v>
-      </c>
-      <c r="G36" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="H36" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I36" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J36" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="K36" s="2" t="inlineStr">
         <is>
           <t>SAR</t>
         </is>

--- a/excel_routes/route_ELQ_CAI_threats.xlsx
+++ b/excel_routes/route_ELQ_CAI_threats.xlsx
@@ -5,10 +5,10 @@
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\CODERED\LAB\Artifacts\outputs\run_generated_260726_at_14.46\reports\excel_routes\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\CODERED\LAB\Artifacts\outputs\run_generated_270726_at_12.25\reports\excel_routes\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2D78E941-A6B5-4AE3-AF77-B95CA165F1EE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9CC130FB-C7DF-4ACF-9927-9BAB57323026}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="12972" yWindow="348" windowWidth="10068" windowHeight="10284" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="521" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="521" uniqueCount="73">
   <si>
     <t>Date</t>
   </si>
@@ -81,6 +81,9 @@
     <t>29-JUL-26</t>
   </si>
   <si>
+    <t>MED</t>
+  </si>
+  <si>
     <t>31-JUL-26</t>
   </si>
   <si>
@@ -141,9 +144,6 @@
     <t>09-SEP-26</t>
   </si>
   <si>
-    <t>11-SEP-26</t>
-  </si>
-  <si>
     <t>15-SEP-26</t>
   </si>
   <si>
@@ -192,9 +192,6 @@
     <t>02-NOV-26</t>
   </si>
   <si>
-    <t>MED</t>
-  </si>
-  <si>
     <t>06-NOV-26</t>
   </si>
   <si>
@@ -216,9 +213,6 @@
     <t>27-NOV-26</t>
   </si>
   <si>
-    <t>28-NOV-26</t>
-  </si>
-  <si>
     <t>30-NOV-26</t>
   </si>
   <si>
@@ -244,6 +238,9 @@
   </si>
   <si>
     <t>25-DEC-26</t>
+  </si>
+  <si>
+    <t>26-DEC-26</t>
   </si>
   <si>
     <t>28-DEC-26</t>
@@ -294,14 +291,14 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF8D7DA"/>
-        <bgColor rgb="FFF8D7DA"/>
+        <fgColor rgb="FFFFF3CD"/>
+        <bgColor rgb="FFFFF3CD"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFF3CD"/>
-        <bgColor rgb="FFFFF3CD"/>
+        <fgColor rgb="FFF8D7DA"/>
+        <bgColor rgb="FFF8D7DA"/>
       </patternFill>
     </fill>
   </fills>
@@ -716,10 +713,10 @@
         <v>400</v>
       </c>
       <c r="E2" s="2">
-        <v>380</v>
+        <v>400</v>
       </c>
       <c r="F2" s="2">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="G2" s="2">
         <v>40</v>
@@ -751,10 +748,10 @@
         <v>401</v>
       </c>
       <c r="E3" s="2">
-        <v>380</v>
+        <v>400</v>
       </c>
       <c r="F3" s="2">
-        <v>21</v>
+        <v>1</v>
       </c>
       <c r="G3" s="2">
         <v>40</v>
@@ -780,16 +777,16 @@
         <v>12</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="D4" s="2">
+        <v>350</v>
+      </c>
+      <c r="E4" s="2">
         <v>400</v>
       </c>
-      <c r="E4" s="2">
-        <v>380</v>
-      </c>
       <c r="F4" s="2">
-        <v>20</v>
+        <v>-50</v>
       </c>
       <c r="G4" s="2">
         <v>40</v>
@@ -800,8 +797,8 @@
       <c r="I4" s="2">
         <v>-10</v>
       </c>
-      <c r="J4" s="3" t="s">
-        <v>14</v>
+      <c r="J4" s="4" t="s">
+        <v>18</v>
       </c>
       <c r="K4" s="2" t="s">
         <v>15</v>
@@ -818,13 +815,13 @@
         <v>16</v>
       </c>
       <c r="D5" s="2">
-        <v>401</v>
+        <v>350</v>
       </c>
       <c r="E5" s="2">
         <v>380</v>
       </c>
       <c r="F5" s="2">
-        <v>21</v>
+        <v>-30</v>
       </c>
       <c r="G5" s="2">
         <v>40</v>
@@ -844,22 +841,22 @@
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="D6" s="2">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="E6" s="2">
         <v>400</v>
       </c>
       <c r="F6" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G6" s="2">
         <v>40</v>
@@ -879,22 +876,22 @@
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="D7" s="2">
-        <v>500</v>
+        <v>400</v>
       </c>
       <c r="E7" s="2">
-        <v>400</v>
+        <v>380</v>
       </c>
       <c r="F7" s="2">
-        <v>100</v>
+        <v>20</v>
       </c>
       <c r="G7" s="2">
         <v>40</v>
@@ -914,22 +911,22 @@
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C8" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="B8" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>13</v>
-      </c>
       <c r="D8" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="E8" s="2">
         <v>400</v>
       </c>
       <c r="F8" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G8" s="2">
         <v>40</v>
@@ -949,7 +946,7 @@
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A9" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>12</v>
@@ -984,22 +981,22 @@
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="D10" s="2">
-        <v>500</v>
+        <v>400</v>
       </c>
       <c r="E10" s="2">
         <v>400</v>
       </c>
       <c r="F10" s="2">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="G10" s="2">
         <v>40</v>
@@ -1025,16 +1022,16 @@
         <v>12</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="D11" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="E11" s="2">
         <v>400</v>
       </c>
       <c r="F11" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G11" s="2">
         <v>40</v>
@@ -1063,13 +1060,13 @@
         <v>16</v>
       </c>
       <c r="D12" s="2">
-        <v>500</v>
+        <v>401</v>
       </c>
       <c r="E12" s="2">
         <v>400</v>
       </c>
       <c r="F12" s="2">
-        <v>100</v>
+        <v>1</v>
       </c>
       <c r="G12" s="2">
         <v>40</v>
@@ -1089,31 +1086,31 @@
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A13" s="2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B13" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="D13" s="2">
-        <v>531</v>
+        <v>400</v>
       </c>
       <c r="E13" s="2">
         <v>400</v>
       </c>
       <c r="F13" s="2">
-        <v>131</v>
+        <v>0</v>
       </c>
       <c r="G13" s="2">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="H13" s="2">
         <v>30</v>
       </c>
       <c r="I13" s="2">
-        <v>-16</v>
+        <v>-10</v>
       </c>
       <c r="J13" s="3" t="s">
         <v>14</v>
@@ -1124,13 +1121,13 @@
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A14" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B14" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="D14" s="2">
         <v>401</v>
@@ -1159,31 +1156,31 @@
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A15" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C15" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="B15" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="C15" s="2" t="s">
-        <v>16</v>
-      </c>
       <c r="D15" s="2">
-        <v>500</v>
+        <v>531</v>
       </c>
       <c r="E15" s="2">
         <v>400</v>
       </c>
       <c r="F15" s="2">
-        <v>100</v>
+        <v>131</v>
       </c>
       <c r="G15" s="2">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="H15" s="2">
         <v>30</v>
       </c>
       <c r="I15" s="2">
-        <v>-10</v>
+        <v>-16</v>
       </c>
       <c r="J15" s="3" t="s">
         <v>14</v>
@@ -1200,16 +1197,16 @@
         <v>12</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="D16" s="2">
+        <v>401</v>
+      </c>
+      <c r="E16" s="2">
         <v>400</v>
       </c>
-      <c r="E16" s="2">
-        <v>380</v>
-      </c>
       <c r="F16" s="2">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="G16" s="2">
         <v>40</v>
@@ -1241,10 +1238,10 @@
         <v>401</v>
       </c>
       <c r="E17" s="2">
-        <v>380</v>
+        <v>400</v>
       </c>
       <c r="F17" s="2">
-        <v>21</v>
+        <v>1</v>
       </c>
       <c r="G17" s="2">
         <v>40</v>
@@ -1308,13 +1305,13 @@
         <v>16</v>
       </c>
       <c r="D19" s="2">
-        <v>500</v>
+        <v>401</v>
       </c>
       <c r="E19" s="2">
         <v>380</v>
       </c>
       <c r="F19" s="2">
-        <v>120</v>
+        <v>21</v>
       </c>
       <c r="G19" s="2">
         <v>40</v>
@@ -1340,16 +1337,16 @@
         <v>12</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="D20" s="2">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="E20" s="2">
-        <v>400</v>
+        <v>380</v>
       </c>
       <c r="F20" s="2">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="G20" s="2">
         <v>40</v>
@@ -1378,13 +1375,13 @@
         <v>16</v>
       </c>
       <c r="D21" s="2">
-        <v>500</v>
+        <v>401</v>
       </c>
       <c r="E21" s="2">
-        <v>400</v>
+        <v>380</v>
       </c>
       <c r="F21" s="2">
-        <v>100</v>
+        <v>21</v>
       </c>
       <c r="G21" s="2">
         <v>40</v>
@@ -1410,16 +1407,16 @@
         <v>12</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="D22" s="2">
+        <v>401</v>
+      </c>
+      <c r="E22" s="2">
         <v>400</v>
       </c>
-      <c r="E22" s="2">
-        <v>380</v>
-      </c>
       <c r="F22" s="2">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="G22" s="2">
         <v>40</v>
@@ -1445,16 +1442,16 @@
         <v>12</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="D23" s="2">
         <v>401</v>
       </c>
       <c r="E23" s="2">
-        <v>380</v>
+        <v>400</v>
       </c>
       <c r="F23" s="2">
-        <v>21</v>
+        <v>1</v>
       </c>
       <c r="G23" s="2">
         <v>40</v>
@@ -1474,22 +1471,22 @@
     </row>
     <row r="24" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A24" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B24" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="D24" s="2">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="E24" s="2">
         <v>380</v>
       </c>
       <c r="F24" s="2">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="G24" s="2">
         <v>40</v>
@@ -1515,16 +1512,16 @@
         <v>12</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="D25" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="E25" s="2">
         <v>380</v>
       </c>
       <c r="F25" s="2">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G25" s="2">
         <v>40</v>
@@ -1550,7 +1547,7 @@
         <v>12</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>29</v>
+        <v>16</v>
       </c>
       <c r="D26" s="2">
         <v>401</v>
@@ -1579,22 +1576,22 @@
     </row>
     <row r="27" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A27" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B27" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="D27" s="2">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="E27" s="2">
         <v>380</v>
       </c>
       <c r="F27" s="2">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="G27" s="2">
         <v>40</v>
@@ -1614,13 +1611,13 @@
     </row>
     <row r="28" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A28" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B28" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D28" s="2">
         <v>401</v>
@@ -1649,22 +1646,22 @@
     </row>
     <row r="29" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A29" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B29" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="D29" s="2">
-        <v>500</v>
+        <v>401</v>
       </c>
       <c r="E29" s="2">
         <v>380</v>
       </c>
       <c r="F29" s="2">
-        <v>120</v>
+        <v>21</v>
       </c>
       <c r="G29" s="2">
         <v>40</v>
@@ -1684,22 +1681,22 @@
     </row>
     <row r="30" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A30" s="2" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B30" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="D30" s="2">
-        <v>500</v>
+        <v>401</v>
       </c>
       <c r="E30" s="2">
         <v>380</v>
       </c>
       <c r="F30" s="2">
-        <v>120</v>
+        <v>21</v>
       </c>
       <c r="G30" s="2">
         <v>40</v>
@@ -1725,16 +1722,16 @@
         <v>12</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="D31" s="2">
-        <v>400</v>
+        <v>500</v>
       </c>
       <c r="E31" s="2">
         <v>380</v>
       </c>
       <c r="F31" s="2">
-        <v>20</v>
+        <v>120</v>
       </c>
       <c r="G31" s="2">
         <v>40</v>
@@ -1760,16 +1757,16 @@
         <v>12</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>29</v>
+        <v>16</v>
       </c>
       <c r="D32" s="2">
-        <v>401</v>
+        <v>500</v>
       </c>
       <c r="E32" s="2">
         <v>380</v>
       </c>
       <c r="F32" s="2">
-        <v>21</v>
+        <v>120</v>
       </c>
       <c r="G32" s="2">
         <v>40</v>
@@ -1789,22 +1786,22 @@
     </row>
     <row r="33" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A33" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B33" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="D33" s="2">
-        <v>500</v>
+        <v>400</v>
       </c>
       <c r="E33" s="2">
         <v>380</v>
       </c>
       <c r="F33" s="2">
-        <v>120</v>
+        <v>20</v>
       </c>
       <c r="G33" s="2">
         <v>40</v>
@@ -1830,16 +1827,16 @@
         <v>12</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>13</v>
+        <v>30</v>
       </c>
       <c r="D34" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="E34" s="2">
         <v>380</v>
       </c>
       <c r="F34" s="2">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G34" s="2">
         <v>40</v>
@@ -1865,16 +1862,16 @@
         <v>12</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="D35" s="2">
-        <v>401</v>
+        <v>500</v>
       </c>
       <c r="E35" s="2">
         <v>380</v>
       </c>
       <c r="F35" s="2">
-        <v>21</v>
+        <v>120</v>
       </c>
       <c r="G35" s="2">
         <v>40</v>
@@ -1894,22 +1891,22 @@
     </row>
     <row r="36" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A36" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B36" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="D36" s="2">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="E36" s="2">
         <v>380</v>
       </c>
       <c r="F36" s="2">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="G36" s="2">
         <v>40</v>
@@ -1935,16 +1932,16 @@
         <v>12</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D37" s="2">
         <v>401</v>
       </c>
       <c r="E37" s="2">
-        <v>400</v>
+        <v>380</v>
       </c>
       <c r="F37" s="2">
-        <v>1</v>
+        <v>21</v>
       </c>
       <c r="G37" s="2">
         <v>40</v>
@@ -1976,10 +1973,10 @@
         <v>401</v>
       </c>
       <c r="E38" s="2">
-        <v>400</v>
+        <v>380</v>
       </c>
       <c r="F38" s="2">
-        <v>1</v>
+        <v>21</v>
       </c>
       <c r="G38" s="2">
         <v>40</v>
@@ -2005,16 +2002,16 @@
         <v>12</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="D39" s="2">
-        <v>450</v>
+        <v>401</v>
       </c>
       <c r="E39" s="2">
-        <v>459</v>
+        <v>400</v>
       </c>
       <c r="F39" s="2">
-        <v>-9</v>
+        <v>1</v>
       </c>
       <c r="G39" s="2">
         <v>40</v>
@@ -2034,7 +2031,7 @@
     </row>
     <row r="40" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A40" s="2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B40" s="2" t="s">
         <v>12</v>
@@ -2046,19 +2043,19 @@
         <v>401</v>
       </c>
       <c r="E40" s="2">
-        <v>412</v>
+        <v>400</v>
       </c>
       <c r="F40" s="2">
-        <v>-11</v>
+        <v>1</v>
       </c>
       <c r="G40" s="2">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="H40" s="2">
         <v>30</v>
       </c>
       <c r="I40" s="2">
-        <v>0</v>
+        <v>-10</v>
       </c>
       <c r="J40" s="3" t="s">
         <v>14</v>
@@ -2081,10 +2078,10 @@
         <v>450</v>
       </c>
       <c r="E41" s="2">
-        <v>412</v>
+        <v>459</v>
       </c>
       <c r="F41" s="2">
-        <v>38</v>
+        <v>-9</v>
       </c>
       <c r="G41" s="2">
         <v>40</v>
@@ -2110,25 +2107,25 @@
         <v>12</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="D42" s="2">
-        <v>550</v>
+        <v>401</v>
       </c>
       <c r="E42" s="2">
-        <v>459</v>
+        <v>412</v>
       </c>
       <c r="F42" s="2">
-        <v>91</v>
+        <v>-11</v>
       </c>
       <c r="G42" s="2">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="H42" s="2">
         <v>30</v>
       </c>
       <c r="I42" s="2">
-        <v>-10</v>
+        <v>0</v>
       </c>
       <c r="J42" s="3" t="s">
         <v>14</v>
@@ -2139,7 +2136,7 @@
     </row>
     <row r="43" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A43" s="2" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B43" s="2" t="s">
         <v>12</v>
@@ -2148,13 +2145,13 @@
         <v>13</v>
       </c>
       <c r="D43" s="2">
-        <v>550</v>
+        <v>450</v>
       </c>
       <c r="E43" s="2">
         <v>412</v>
       </c>
       <c r="F43" s="2">
-        <v>138</v>
+        <v>38</v>
       </c>
       <c r="G43" s="2">
         <v>40</v>
@@ -2174,31 +2171,31 @@
     </row>
     <row r="44" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A44" s="2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B44" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="D44" s="2">
-        <v>401</v>
+        <v>550</v>
       </c>
       <c r="E44" s="2">
-        <v>412</v>
+        <v>459</v>
       </c>
       <c r="F44" s="2">
-        <v>-11</v>
+        <v>91</v>
       </c>
       <c r="G44" s="2">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="H44" s="2">
         <v>30</v>
       </c>
       <c r="I44" s="2">
-        <v>0</v>
+        <v>-10</v>
       </c>
       <c r="J44" s="3" t="s">
         <v>14</v>
@@ -2215,25 +2212,25 @@
         <v>12</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="D45" s="2">
-        <v>401</v>
+        <v>550</v>
       </c>
       <c r="E45" s="2">
         <v>412</v>
       </c>
       <c r="F45" s="2">
-        <v>-11</v>
+        <v>138</v>
       </c>
       <c r="G45" s="2">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="H45" s="2">
         <v>30</v>
       </c>
       <c r="I45" s="2">
-        <v>0</v>
+        <v>-10</v>
       </c>
       <c r="J45" s="3" t="s">
         <v>14</v>
@@ -2256,10 +2253,10 @@
         <v>450</v>
       </c>
       <c r="E46" s="2">
-        <v>412</v>
+        <v>390</v>
       </c>
       <c r="F46" s="2">
-        <v>38</v>
+        <v>60</v>
       </c>
       <c r="G46" s="2">
         <v>40</v>
@@ -2355,7 +2352,7 @@
         <v>12</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D49" s="2">
         <v>401</v>
@@ -2428,13 +2425,13 @@
         <v>13</v>
       </c>
       <c r="D51" s="2">
-        <v>450</v>
+        <v>500</v>
       </c>
       <c r="E51" s="2">
         <v>412</v>
       </c>
       <c r="F51" s="2">
-        <v>38</v>
+        <v>88</v>
       </c>
       <c r="G51" s="2">
         <v>40</v>
@@ -2530,7 +2527,7 @@
         <v>12</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D54" s="2">
         <v>401</v>
@@ -2705,7 +2702,7 @@
         <v>12</v>
       </c>
       <c r="C59" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D59" s="2">
         <v>401</v>
@@ -2848,13 +2845,13 @@
         <v>51</v>
       </c>
       <c r="D63" s="2">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="E63" s="2">
         <v>2295</v>
       </c>
       <c r="F63" s="2">
-        <v>-1904</v>
+        <v>-1905</v>
       </c>
       <c r="G63" s="2">
         <v>20</v>
@@ -2865,7 +2862,7 @@
       <c r="I63" s="2">
         <v>10</v>
       </c>
-      <c r="J63" s="4" t="s">
+      <c r="J63" s="5" t="s">
         <v>52</v>
       </c>
       <c r="K63" s="2" t="s">
@@ -2900,7 +2897,7 @@
       <c r="I64" s="2">
         <v>0</v>
       </c>
-      <c r="J64" s="4" t="s">
+      <c r="J64" s="5" t="s">
         <v>52</v>
       </c>
       <c r="K64" s="2" t="s">
@@ -2915,7 +2912,7 @@
         <v>12</v>
       </c>
       <c r="C65" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D65" s="2">
         <v>556</v>
@@ -2935,7 +2932,7 @@
       <c r="I65" s="2">
         <v>7</v>
       </c>
-      <c r="J65" s="4" t="s">
+      <c r="J65" s="5" t="s">
         <v>52</v>
       </c>
       <c r="K65" s="2" t="s">
@@ -2970,7 +2967,7 @@
       <c r="I66" s="2">
         <v>0</v>
       </c>
-      <c r="J66" s="4" t="s">
+      <c r="J66" s="5" t="s">
         <v>52</v>
       </c>
       <c r="K66" s="2" t="s">
@@ -2985,27 +2982,27 @@
         <v>12</v>
       </c>
       <c r="C67" s="2" t="s">
-        <v>22</v>
+        <v>51</v>
       </c>
       <c r="D67" s="2">
-        <v>556</v>
+        <v>409</v>
       </c>
       <c r="E67" s="2">
         <v>2295</v>
       </c>
       <c r="F67" s="2">
-        <v>-1739</v>
+        <v>-1886</v>
       </c>
       <c r="G67" s="2">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="H67" s="2">
         <v>30</v>
       </c>
       <c r="I67" s="2">
-        <v>7</v>
-      </c>
-      <c r="J67" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="J67" s="5" t="s">
         <v>52</v>
       </c>
       <c r="K67" s="2" t="s">
@@ -3020,27 +3017,27 @@
         <v>12</v>
       </c>
       <c r="C68" s="2" t="s">
-        <v>51</v>
+        <v>23</v>
       </c>
       <c r="D68" s="2">
-        <v>637</v>
+        <v>556</v>
       </c>
       <c r="E68" s="2">
         <v>2295</v>
       </c>
       <c r="F68" s="2">
-        <v>-1658</v>
+        <v>-1739</v>
       </c>
       <c r="G68" s="2">
-        <v>40</v>
+        <v>23</v>
       </c>
       <c r="H68" s="2">
         <v>30</v>
       </c>
       <c r="I68" s="2">
-        <v>-10</v>
-      </c>
-      <c r="J68" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="J68" s="5" t="s">
         <v>52</v>
       </c>
       <c r="K68" s="2" t="s">
@@ -3075,8 +3072,8 @@
       <c r="I69" s="2">
         <v>0</v>
       </c>
-      <c r="J69" s="5" t="s">
-        <v>55</v>
+      <c r="J69" s="4" t="s">
+        <v>18</v>
       </c>
       <c r="K69" s="2" t="s">
         <v>15</v>
@@ -3084,7 +3081,7 @@
     </row>
     <row r="70" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A70" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B70" s="2" t="s">
         <v>12</v>
@@ -3110,8 +3107,8 @@
       <c r="I70" s="2">
         <v>0</v>
       </c>
-      <c r="J70" s="5" t="s">
-        <v>55</v>
+      <c r="J70" s="4" t="s">
+        <v>18</v>
       </c>
       <c r="K70" s="2" t="s">
         <v>15</v>
@@ -3119,33 +3116,33 @@
     </row>
     <row r="71" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A71" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B71" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C71" s="2" t="s">
-        <v>51</v>
+        <v>23</v>
       </c>
       <c r="D71" s="2">
-        <v>410</v>
+        <v>556</v>
       </c>
       <c r="E71" s="2">
         <v>2295</v>
       </c>
       <c r="F71" s="2">
-        <v>-1885</v>
+        <v>-1739</v>
       </c>
       <c r="G71" s="2">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="H71" s="2">
         <v>30</v>
       </c>
       <c r="I71" s="2">
-        <v>10</v>
-      </c>
-      <c r="J71" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="J71" s="5" t="s">
         <v>52</v>
       </c>
       <c r="K71" s="2" t="s">
@@ -3154,33 +3151,33 @@
     </row>
     <row r="72" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A72" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B72" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C72" s="2" t="s">
-        <v>22</v>
+        <v>51</v>
       </c>
       <c r="D72" s="2">
-        <v>556</v>
+        <v>634</v>
       </c>
       <c r="E72" s="2">
         <v>2295</v>
       </c>
       <c r="F72" s="2">
-        <v>-1739</v>
+        <v>-1661</v>
       </c>
       <c r="G72" s="2">
-        <v>23</v>
+        <v>40</v>
       </c>
       <c r="H72" s="2">
         <v>30</v>
       </c>
       <c r="I72" s="2">
-        <v>7</v>
-      </c>
-      <c r="J72" s="4" t="s">
+        <v>-10</v>
+      </c>
+      <c r="J72" s="5" t="s">
         <v>52</v>
       </c>
       <c r="K72" s="2" t="s">
@@ -3189,7 +3186,7 @@
     </row>
     <row r="73" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A73" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B73" s="2" t="s">
         <v>12</v>
@@ -3215,8 +3212,8 @@
       <c r="I73" s="2">
         <v>0</v>
       </c>
-      <c r="J73" s="5" t="s">
-        <v>55</v>
+      <c r="J73" s="4" t="s">
+        <v>18</v>
       </c>
       <c r="K73" s="2" t="s">
         <v>15</v>
@@ -3224,7 +3221,7 @@
     </row>
     <row r="74" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A74" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B74" s="2" t="s">
         <v>12</v>
@@ -3250,8 +3247,8 @@
       <c r="I74" s="2">
         <v>0</v>
       </c>
-      <c r="J74" s="5" t="s">
-        <v>55</v>
+      <c r="J74" s="4" t="s">
+        <v>18</v>
       </c>
       <c r="K74" s="2" t="s">
         <v>15</v>
@@ -3259,33 +3256,33 @@
     </row>
     <row r="75" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A75" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B75" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C75" s="2" t="s">
-        <v>22</v>
+        <v>51</v>
       </c>
       <c r="D75" s="2">
-        <v>556</v>
+        <v>409</v>
       </c>
       <c r="E75" s="2">
         <v>2295</v>
       </c>
       <c r="F75" s="2">
-        <v>-1739</v>
+        <v>-1886</v>
       </c>
       <c r="G75" s="2">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="H75" s="2">
         <v>30</v>
       </c>
       <c r="I75" s="2">
-        <v>7</v>
-      </c>
-      <c r="J75" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="J75" s="5" t="s">
         <v>52</v>
       </c>
       <c r="K75" s="2" t="s">
@@ -3294,33 +3291,33 @@
     </row>
     <row r="76" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A76" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B76" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C76" s="2" t="s">
-        <v>51</v>
+        <v>23</v>
       </c>
       <c r="D76" s="2">
-        <v>636</v>
+        <v>556</v>
       </c>
       <c r="E76" s="2">
         <v>2295</v>
       </c>
       <c r="F76" s="2">
-        <v>-1659</v>
+        <v>-1739</v>
       </c>
       <c r="G76" s="2">
-        <v>40</v>
+        <v>23</v>
       </c>
       <c r="H76" s="2">
         <v>30</v>
       </c>
       <c r="I76" s="2">
-        <v>-10</v>
-      </c>
-      <c r="J76" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="J76" s="5" t="s">
         <v>52</v>
       </c>
       <c r="K76" s="2" t="s">
@@ -3329,7 +3326,7 @@
     </row>
     <row r="77" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A77" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B77" s="2" t="s">
         <v>12</v>
@@ -3355,8 +3352,8 @@
       <c r="I77" s="2">
         <v>0</v>
       </c>
-      <c r="J77" s="5" t="s">
-        <v>55</v>
+      <c r="J77" s="4" t="s">
+        <v>18</v>
       </c>
       <c r="K77" s="2" t="s">
         <v>15</v>
@@ -3364,7 +3361,7 @@
     </row>
     <row r="78" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A78" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B78" s="2" t="s">
         <v>12</v>
@@ -3390,8 +3387,8 @@
       <c r="I78" s="2">
         <v>0</v>
       </c>
-      <c r="J78" s="5" t="s">
-        <v>55</v>
+      <c r="J78" s="4" t="s">
+        <v>18</v>
       </c>
       <c r="K78" s="2" t="s">
         <v>15</v>
@@ -3399,7 +3396,7 @@
     </row>
     <row r="79" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A79" s="2" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B79" s="2" t="s">
         <v>12</v>
@@ -3408,13 +3405,13 @@
         <v>51</v>
       </c>
       <c r="D79" s="2">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="E79" s="2">
         <v>2295</v>
       </c>
       <c r="F79" s="2">
-        <v>-1885</v>
+        <v>-1886</v>
       </c>
       <c r="G79" s="2">
         <v>20</v>
@@ -3425,7 +3422,7 @@
       <c r="I79" s="2">
         <v>10</v>
       </c>
-      <c r="J79" s="4" t="s">
+      <c r="J79" s="5" t="s">
         <v>52</v>
       </c>
       <c r="K79" s="2" t="s">
@@ -3434,13 +3431,13 @@
     </row>
     <row r="80" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A80" s="2" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B80" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C80" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D80" s="2">
         <v>831</v>
@@ -3460,7 +3457,7 @@
       <c r="I80" s="2">
         <v>-16</v>
       </c>
-      <c r="J80" s="4" t="s">
+      <c r="J80" s="5" t="s">
         <v>52</v>
       </c>
       <c r="K80" s="2" t="s">
@@ -3469,7 +3466,7 @@
     </row>
     <row r="81" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A81" s="2" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B81" s="2" t="s">
         <v>12</v>
@@ -3495,8 +3492,8 @@
       <c r="I81" s="2">
         <v>0</v>
       </c>
-      <c r="J81" s="5" t="s">
-        <v>55</v>
+      <c r="J81" s="4" t="s">
+        <v>18</v>
       </c>
       <c r="K81" s="2" t="s">
         <v>15</v>
@@ -3504,7 +3501,7 @@
     </row>
     <row r="82" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A82" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B82" s="2" t="s">
         <v>12</v>
@@ -3530,8 +3527,8 @@
       <c r="I82" s="2">
         <v>0</v>
       </c>
-      <c r="J82" s="5" t="s">
-        <v>55</v>
+      <c r="J82" s="4" t="s">
+        <v>18</v>
       </c>
       <c r="K82" s="2" t="s">
         <v>15</v>
@@ -3539,7 +3536,7 @@
     </row>
     <row r="83" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A83" s="2" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B83" s="2" t="s">
         <v>12</v>
@@ -3548,25 +3545,25 @@
         <v>51</v>
       </c>
       <c r="D83" s="2">
-        <v>642</v>
+        <v>409</v>
       </c>
       <c r="E83" s="2">
-        <v>519</v>
+        <v>2295</v>
       </c>
       <c r="F83" s="2">
-        <v>123</v>
+        <v>-1886</v>
       </c>
       <c r="G83" s="2">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="H83" s="2">
         <v>30</v>
       </c>
       <c r="I83" s="2">
-        <v>-10</v>
-      </c>
-      <c r="J83" s="3" t="s">
-        <v>14</v>
+        <v>10</v>
+      </c>
+      <c r="J83" s="5" t="s">
+        <v>52</v>
       </c>
       <c r="K83" s="2" t="s">
         <v>15</v>
@@ -3574,33 +3571,33 @@
     </row>
     <row r="84" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A84" s="2" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="B84" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C84" s="2" t="s">
-        <v>51</v>
+        <v>23</v>
       </c>
       <c r="D84" s="2">
-        <v>410</v>
+        <v>556</v>
       </c>
       <c r="E84" s="2">
         <v>2295</v>
       </c>
       <c r="F84" s="2">
-        <v>-1885</v>
+        <v>-1739</v>
       </c>
       <c r="G84" s="2">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="H84" s="2">
         <v>30</v>
       </c>
       <c r="I84" s="2">
-        <v>10</v>
-      </c>
-      <c r="J84" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="J84" s="5" t="s">
         <v>52</v>
       </c>
       <c r="K84" s="2" t="s">
@@ -3609,34 +3606,34 @@
     </row>
     <row r="85" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A85" s="2" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="B85" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C85" s="2" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="D85" s="2">
-        <v>556</v>
+        <v>2050</v>
       </c>
       <c r="E85" s="2">
         <v>2295</v>
       </c>
       <c r="F85" s="2">
-        <v>-1739</v>
+        <v>-245</v>
       </c>
       <c r="G85" s="2">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="H85" s="2">
         <v>30</v>
       </c>
       <c r="I85" s="2">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="J85" s="4" t="s">
-        <v>52</v>
+        <v>18</v>
       </c>
       <c r="K85" s="2" t="s">
         <v>15</v>
@@ -3644,7 +3641,7 @@
     </row>
     <row r="86" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A86" s="2" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B86" s="2" t="s">
         <v>12</v>
@@ -3670,8 +3667,8 @@
       <c r="I86" s="2">
         <v>0</v>
       </c>
-      <c r="J86" s="5" t="s">
-        <v>55</v>
+      <c r="J86" s="4" t="s">
+        <v>18</v>
       </c>
       <c r="K86" s="2" t="s">
         <v>15</v>
@@ -3679,34 +3676,34 @@
     </row>
     <row r="87" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A87" s="2" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B87" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C87" s="2" t="s">
-        <v>16</v>
+        <v>51</v>
       </c>
       <c r="D87" s="2">
-        <v>2050</v>
+        <v>409</v>
       </c>
       <c r="E87" s="2">
         <v>2295</v>
       </c>
       <c r="F87" s="2">
-        <v>-245</v>
+        <v>-1886</v>
       </c>
       <c r="G87" s="2">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="H87" s="2">
         <v>30</v>
       </c>
       <c r="I87" s="2">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="J87" s="5" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="K87" s="2" t="s">
         <v>15</v>
@@ -3714,33 +3711,33 @@
     </row>
     <row r="88" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A88" s="2" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="B88" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C88" s="2" t="s">
-        <v>51</v>
+        <v>23</v>
       </c>
       <c r="D88" s="2">
-        <v>410</v>
+        <v>556</v>
       </c>
       <c r="E88" s="2">
         <v>2295</v>
       </c>
       <c r="F88" s="2">
-        <v>-1885</v>
+        <v>-1739</v>
       </c>
       <c r="G88" s="2">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="H88" s="2">
         <v>30</v>
       </c>
       <c r="I88" s="2">
-        <v>10</v>
-      </c>
-      <c r="J88" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="J88" s="5" t="s">
         <v>52</v>
       </c>
       <c r="K88" s="2" t="s">
@@ -3749,34 +3746,34 @@
     </row>
     <row r="89" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A89" s="2" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="B89" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C89" s="2" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="D89" s="2">
-        <v>556</v>
+        <v>2050</v>
       </c>
       <c r="E89" s="2">
         <v>2295</v>
       </c>
       <c r="F89" s="2">
-        <v>-1739</v>
+        <v>-245</v>
       </c>
       <c r="G89" s="2">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="H89" s="2">
         <v>30</v>
       </c>
       <c r="I89" s="2">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="J89" s="4" t="s">
-        <v>52</v>
+        <v>18</v>
       </c>
       <c r="K89" s="2" t="s">
         <v>15</v>
@@ -3784,7 +3781,7 @@
     </row>
     <row r="90" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A90" s="2" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B90" s="2" t="s">
         <v>12</v>
@@ -3810,8 +3807,8 @@
       <c r="I90" s="2">
         <v>0</v>
       </c>
-      <c r="J90" s="5" t="s">
-        <v>55</v>
+      <c r="J90" s="4" t="s">
+        <v>18</v>
       </c>
       <c r="K90" s="2" t="s">
         <v>15</v>
@@ -3819,34 +3816,34 @@
     </row>
     <row r="91" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A91" s="2" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B91" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C91" s="2" t="s">
-        <v>16</v>
+        <v>51</v>
       </c>
       <c r="D91" s="2">
-        <v>2050</v>
+        <v>409</v>
       </c>
       <c r="E91" s="2">
         <v>2295</v>
       </c>
       <c r="F91" s="2">
-        <v>-245</v>
+        <v>-1886</v>
       </c>
       <c r="G91" s="2">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="H91" s="2">
         <v>30</v>
       </c>
       <c r="I91" s="2">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="J91" s="5" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="K91" s="2" t="s">
         <v>15</v>
@@ -3854,33 +3851,33 @@
     </row>
     <row r="92" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A92" s="2" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="B92" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C92" s="2" t="s">
-        <v>51</v>
+        <v>23</v>
       </c>
       <c r="D92" s="2">
-        <v>410</v>
+        <v>556</v>
       </c>
       <c r="E92" s="2">
         <v>2295</v>
       </c>
       <c r="F92" s="2">
-        <v>-1885</v>
+        <v>-1739</v>
       </c>
       <c r="G92" s="2">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="H92" s="2">
         <v>30</v>
       </c>
       <c r="I92" s="2">
-        <v>10</v>
-      </c>
-      <c r="J92" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="J92" s="5" t="s">
         <v>52</v>
       </c>
       <c r="K92" s="2" t="s">
@@ -3889,34 +3886,34 @@
     </row>
     <row r="93" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A93" s="2" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="B93" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C93" s="2" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="D93" s="2">
-        <v>556</v>
+        <v>2050</v>
       </c>
       <c r="E93" s="2">
         <v>2295</v>
       </c>
       <c r="F93" s="2">
-        <v>-1739</v>
+        <v>-245</v>
       </c>
       <c r="G93" s="2">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="H93" s="2">
         <v>30</v>
       </c>
       <c r="I93" s="2">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="J93" s="4" t="s">
-        <v>52</v>
+        <v>18</v>
       </c>
       <c r="K93" s="2" t="s">
         <v>15</v>
@@ -3924,7 +3921,7 @@
     </row>
     <row r="94" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A94" s="2" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B94" s="2" t="s">
         <v>12</v>
@@ -3950,8 +3947,8 @@
       <c r="I94" s="2">
         <v>0</v>
       </c>
-      <c r="J94" s="5" t="s">
-        <v>55</v>
+      <c r="J94" s="4" t="s">
+        <v>18</v>
       </c>
       <c r="K94" s="2" t="s">
         <v>15</v>
@@ -3959,34 +3956,34 @@
     </row>
     <row r="95" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A95" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B95" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C95" s="2" t="s">
-        <v>16</v>
+        <v>51</v>
       </c>
       <c r="D95" s="2">
-        <v>2050</v>
+        <v>640</v>
       </c>
       <c r="E95" s="2">
-        <v>2295</v>
+        <v>519</v>
       </c>
       <c r="F95" s="2">
-        <v>-245</v>
+        <v>121</v>
       </c>
       <c r="G95" s="2">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="H95" s="2">
         <v>30</v>
       </c>
       <c r="I95" s="2">
-        <v>0</v>
-      </c>
-      <c r="J95" s="5" t="s">
-        <v>55</v>
+        <v>-10</v>
+      </c>
+      <c r="J95" s="3" t="s">
+        <v>14</v>
       </c>
       <c r="K95" s="2" t="s">
         <v>15</v>
@@ -3994,34 +3991,34 @@
     </row>
     <row r="96" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A96" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B96" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C96" s="2" t="s">
-        <v>51</v>
+        <v>23</v>
       </c>
       <c r="D96" s="2">
-        <v>642</v>
+        <v>556</v>
       </c>
       <c r="E96" s="2">
-        <v>519</v>
+        <v>2295</v>
       </c>
       <c r="F96" s="2">
-        <v>123</v>
+        <v>-1739</v>
       </c>
       <c r="G96" s="2">
-        <v>40</v>
+        <v>23</v>
       </c>
       <c r="H96" s="2">
         <v>30</v>
       </c>
       <c r="I96" s="2">
-        <v>-10</v>
-      </c>
-      <c r="J96" s="3" t="s">
-        <v>14</v>
+        <v>7</v>
+      </c>
+      <c r="J96" s="5" t="s">
+        <v>52</v>
       </c>
       <c r="K96" s="2" t="s">
         <v>15</v>
@@ -4029,7 +4026,7 @@
     </row>
     <row r="97" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A97" s="2" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="B97" s="2" t="s">
         <v>12</v>
@@ -4038,24 +4035,24 @@
         <v>51</v>
       </c>
       <c r="D97" s="2">
-        <v>410</v>
+        <v>634</v>
       </c>
       <c r="E97" s="2">
         <v>2295</v>
       </c>
       <c r="F97" s="2">
-        <v>-1885</v>
+        <v>-1661</v>
       </c>
       <c r="G97" s="2">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="H97" s="2">
         <v>30</v>
       </c>
       <c r="I97" s="2">
-        <v>10</v>
-      </c>
-      <c r="J97" s="4" t="s">
+        <v>-10</v>
+      </c>
+      <c r="J97" s="5" t="s">
         <v>52</v>
       </c>
       <c r="K97" s="2" t="s">
@@ -4064,34 +4061,34 @@
     </row>
     <row r="98" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A98" s="2" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="B98" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C98" s="2" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="D98" s="2">
-        <v>556</v>
+        <v>2050</v>
       </c>
       <c r="E98" s="2">
         <v>2295</v>
       </c>
       <c r="F98" s="2">
-        <v>-1739</v>
+        <v>-245</v>
       </c>
       <c r="G98" s="2">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="H98" s="2">
         <v>30</v>
       </c>
       <c r="I98" s="2">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="J98" s="4" t="s">
-        <v>52</v>
+        <v>18</v>
       </c>
       <c r="K98" s="2" t="s">
         <v>15</v>
@@ -4099,7 +4096,7 @@
     </row>
     <row r="99" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A99" s="2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B99" s="2" t="s">
         <v>12</v>
@@ -4125,8 +4122,8 @@
       <c r="I99" s="2">
         <v>0</v>
       </c>
-      <c r="J99" s="5" t="s">
-        <v>55</v>
+      <c r="J99" s="4" t="s">
+        <v>18</v>
       </c>
       <c r="K99" s="2" t="s">
         <v>15</v>
@@ -4134,34 +4131,34 @@
     </row>
     <row r="100" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A100" s="2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B100" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C100" s="2" t="s">
-        <v>16</v>
+        <v>51</v>
       </c>
       <c r="D100" s="2">
-        <v>2050</v>
+        <v>640</v>
       </c>
       <c r="E100" s="2">
-        <v>2295</v>
+        <v>519</v>
       </c>
       <c r="F100" s="2">
-        <v>-245</v>
+        <v>121</v>
       </c>
       <c r="G100" s="2">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="H100" s="2">
         <v>30</v>
       </c>
       <c r="I100" s="2">
-        <v>0</v>
-      </c>
-      <c r="J100" s="5" t="s">
-        <v>55</v>
+        <v>-10</v>
+      </c>
+      <c r="J100" s="3" t="s">
+        <v>14</v>
       </c>
       <c r="K100" s="2" t="s">
         <v>15</v>
@@ -4169,7 +4166,7 @@
     </row>
     <row r="101" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A101" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B101" s="2" t="s">
         <v>12</v>
@@ -4178,13 +4175,13 @@
         <v>51</v>
       </c>
       <c r="D101" s="2">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="E101" s="2">
         <v>2295</v>
       </c>
       <c r="F101" s="2">
-        <v>-1885</v>
+        <v>-1886</v>
       </c>
       <c r="G101" s="2">
         <v>20</v>
@@ -4195,7 +4192,7 @@
       <c r="I101" s="2">
         <v>10</v>
       </c>
-      <c r="J101" s="4" t="s">
+      <c r="J101" s="5" t="s">
         <v>52</v>
       </c>
       <c r="K101" s="2" t="s">
@@ -4204,13 +4201,13 @@
     </row>
     <row r="102" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A102" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B102" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C102" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D102" s="2">
         <v>556</v>
@@ -4230,7 +4227,7 @@
       <c r="I102" s="2">
         <v>7</v>
       </c>
-      <c r="J102" s="4" t="s">
+      <c r="J102" s="5" t="s">
         <v>52</v>
       </c>
       <c r="K102" s="2" t="s">
@@ -4239,7 +4236,7 @@
     </row>
     <row r="103" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A103" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B103" s="2" t="s">
         <v>12</v>
@@ -4265,8 +4262,8 @@
       <c r="I103" s="2">
         <v>0</v>
       </c>
-      <c r="J103" s="5" t="s">
-        <v>55</v>
+      <c r="J103" s="4" t="s">
+        <v>18</v>
       </c>
       <c r="K103" s="2" t="s">
         <v>15</v>
